--- a/sin_patrones.xlsx
+++ b/sin_patrones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Avances_Tesis_FCB\Script_analisis_GLM\Script GLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457E79B0-71A1-4AD0-9C86-A9F366F1729E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E7672A-C80C-4785-839C-71C68C1F2B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A02DA300-8EA0-4CC6-8739-25F8F4A91BC5}"/>
   </bookViews>
@@ -36,23 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>sample</t>
   </si>
   <si>
-    <t>T_den</t>
-  </si>
-  <si>
-    <t>T_fue</t>
-  </si>
-  <si>
-    <t>H_den</t>
-  </si>
-  <si>
-    <t>H_fue</t>
-  </si>
-  <si>
     <t>Pen</t>
   </si>
   <si>
@@ -111,6 +99,12 @@
   </si>
   <si>
     <t>S15</t>
+  </si>
+  <si>
+    <t>V_te</t>
+  </si>
+  <si>
+    <t>V_hu</t>
   </si>
 </sst>
 </file>
@@ -155,10 +149,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,522 +488,425 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B0D2D6-B11C-4A0B-A56C-C0F17EB0640F}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.5703125" style="1" customWidth="1"/>
-    <col min="4" max="10" width="11.42578125" style="1"/>
+    <col min="3" max="8" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="1">
-        <v>23.580000000000002</v>
-      </c>
-      <c r="D2" s="1">
-        <v>27.22</v>
-      </c>
-      <c r="E2" s="1">
-        <v>55.3</v>
-      </c>
-      <c r="F2" s="1">
-        <v>54.1</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="C2" s="3">
+        <v>3.639999999999997</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1.1999999999999957</v>
+      </c>
+      <c r="E2" s="3">
         <v>18.36</v>
       </c>
+      <c r="F2" s="2">
+        <v>20</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.71599999999999997</v>
+      </c>
       <c r="H2" s="2">
-        <v>20</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.71599999999999997</v>
-      </c>
-      <c r="J2" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="1">
-        <v>23.779999999999998</v>
-      </c>
-      <c r="D3" s="1">
-        <v>27.419999999999998</v>
-      </c>
-      <c r="E3" s="1">
-        <v>52.319999999999993</v>
-      </c>
-      <c r="F3" s="1">
-        <v>51.6</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="C3" s="3">
+        <v>3.6400000000000006</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.71999999999999176</v>
+      </c>
+      <c r="E3" s="3">
         <v>13.36</v>
       </c>
+      <c r="F3" s="2">
+        <v>58.2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.752</v>
+      </c>
       <c r="H3" s="2">
-        <v>58.2</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.752</v>
-      </c>
-      <c r="J3" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" s="1">
-        <v>23.924999999999997</v>
-      </c>
-      <c r="D4" s="1">
-        <v>27.3</v>
-      </c>
-      <c r="E4" s="1">
-        <v>52.3</v>
-      </c>
-      <c r="F4" s="1">
-        <v>52.174999999999997</v>
-      </c>
-      <c r="G4" s="1">
+      <c r="C4" s="3">
+        <v>3.3750000000000036</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="E4" s="3">
         <v>16.600000000000001</v>
       </c>
+      <c r="F4" s="2">
+        <v>37.5</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.89500000000000002</v>
+      </c>
       <c r="H4" s="2">
-        <v>37.5</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.89500000000000002</v>
-      </c>
-      <c r="J4" s="2">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" s="1">
-        <v>24.275000000000002</v>
-      </c>
-      <c r="D5" s="1">
-        <v>26.95</v>
-      </c>
-      <c r="E5" s="1">
-        <v>53.2</v>
-      </c>
-      <c r="F5" s="1">
-        <v>53.625</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="C5" s="3">
+        <v>2.6749999999999972</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.42499999999999716</v>
+      </c>
+      <c r="E5" s="3">
         <v>14</v>
       </c>
+      <c r="F5" s="2">
+        <v>24</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1.0925</v>
+      </c>
       <c r="H5" s="2">
-        <v>24</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.0925</v>
-      </c>
-      <c r="J5" s="2">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="1">
-        <v>24.339999999999996</v>
-      </c>
-      <c r="D6" s="1">
-        <v>27.020000000000003</v>
-      </c>
-      <c r="E6" s="1">
-        <v>52.160000000000004</v>
-      </c>
-      <c r="F6" s="1">
-        <v>52.14</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="C6" s="3">
+        <v>2.6800000000000068</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.0000000000003126E-2</v>
+      </c>
+      <c r="E6" s="3">
         <v>10.739999999999998</v>
       </c>
+      <c r="F6" s="2">
+        <v>53.4</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.39600000000000002</v>
+      </c>
       <c r="H6" s="2">
-        <v>53.4</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.39600000000000002</v>
-      </c>
-      <c r="J6" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="1">
-        <v>24.04</v>
-      </c>
-      <c r="D7" s="1">
-        <v>26.740000000000002</v>
-      </c>
-      <c r="E7" s="1">
-        <v>53.56</v>
-      </c>
-      <c r="F7" s="1">
-        <v>53.839999999999996</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="C7" s="3">
+        <v>2.7000000000000028</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.27999999999999403</v>
+      </c>
+      <c r="E7" s="3">
         <v>7.76</v>
       </c>
+      <c r="F7" s="2">
+        <v>17.2</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.8</v>
+      </c>
       <c r="H7" s="2">
-        <v>17.2</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="J7" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" s="1">
-        <v>22.32</v>
-      </c>
-      <c r="D8" s="1">
-        <v>24.44</v>
-      </c>
-      <c r="E8" s="1">
-        <v>61.42</v>
-      </c>
-      <c r="F8" s="1">
-        <v>60.7</v>
-      </c>
-      <c r="G8" s="1">
+      <c r="C8" s="3">
+        <v>2.120000000000001</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.71999999999999886</v>
+      </c>
+      <c r="E8" s="3">
         <v>19.2</v>
       </c>
+      <c r="F8" s="2">
+        <v>26.6</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.56600000000000006</v>
+      </c>
       <c r="H8" s="2">
-        <v>26.6</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0.56600000000000006</v>
-      </c>
-      <c r="J8" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" s="1">
-        <v>23</v>
-      </c>
-      <c r="D9" s="1">
-        <v>25.619999999999997</v>
-      </c>
-      <c r="E9" s="1">
-        <v>57.8</v>
-      </c>
-      <c r="F9" s="1">
-        <v>57.56</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="C9" s="3">
+        <v>2.6199999999999974</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.23999999999999488</v>
+      </c>
+      <c r="E9" s="3">
         <v>15.419999999999998</v>
       </c>
+      <c r="F9" s="2">
+        <v>43.8</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.42000000000000004</v>
+      </c>
       <c r="H9" s="2">
-        <v>43.8</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0.42000000000000004</v>
-      </c>
-      <c r="J9" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>9</v>
       </c>
-      <c r="C10" s="1">
-        <v>23.15</v>
-      </c>
-      <c r="D10" s="1">
-        <v>26.85</v>
-      </c>
-      <c r="E10" s="1">
-        <v>54.45</v>
-      </c>
-      <c r="F10" s="1">
-        <v>54.55</v>
-      </c>
-      <c r="G10" s="1">
+      <c r="C10" s="3">
+        <v>3.7000000000000028</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9.9999999999994316E-2</v>
+      </c>
+      <c r="E10" s="3">
         <v>15</v>
       </c>
+      <c r="F10" s="2">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.625</v>
+      </c>
       <c r="H10" s="2">
-        <v>3</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="J10" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11" s="1">
-        <v>24.080000000000002</v>
-      </c>
-      <c r="D11" s="1">
-        <v>25.639999999999997</v>
-      </c>
-      <c r="E11" s="1">
-        <v>56.98</v>
-      </c>
-      <c r="F11" s="1">
-        <v>57.040000000000006</v>
-      </c>
-      <c r="G11" s="1">
+      <c r="C11" s="3">
+        <v>1.5599999999999952</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6.0000000000009379E-2</v>
+      </c>
+      <c r="E11" s="3">
         <v>8.9</v>
       </c>
+      <c r="F11" s="2">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.20400000000000001</v>
+      </c>
       <c r="H11" s="2">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0.20400000000000001</v>
-      </c>
-      <c r="J11" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>11</v>
       </c>
-      <c r="C12" s="1">
-        <v>22.7</v>
-      </c>
-      <c r="D12" s="1">
-        <v>25.479999999999997</v>
-      </c>
-      <c r="E12" s="1">
-        <v>58.42</v>
-      </c>
-      <c r="F12" s="1">
-        <v>58.08</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="C12" s="3">
+        <v>2.7799999999999976</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.34000000000000341</v>
+      </c>
+      <c r="E12" s="3">
         <v>15.819999999999999</v>
       </c>
+      <c r="F12" s="2">
+        <v>24.4</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.61199999999999999</v>
+      </c>
       <c r="H12" s="2">
-        <v>24.4</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0.61199999999999999</v>
-      </c>
-      <c r="J12" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>12</v>
       </c>
-      <c r="C13" s="1">
-        <v>23.75</v>
-      </c>
-      <c r="D13" s="1">
-        <v>26.75</v>
-      </c>
-      <c r="E13" s="1">
-        <v>53.7</v>
-      </c>
-      <c r="F13" s="1">
-        <v>53.95</v>
-      </c>
-      <c r="G13" s="1">
+      <c r="C13" s="3">
+        <v>3</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E13" s="3">
         <v>12.2</v>
       </c>
+      <c r="F13" s="2">
+        <v>11</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.91500000000000004</v>
+      </c>
       <c r="H13" s="2">
-        <v>11</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0.91500000000000004</v>
-      </c>
-      <c r="J13" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>13</v>
       </c>
-      <c r="C14" s="1">
-        <v>31.920000000000005</v>
-      </c>
-      <c r="D14" s="1">
-        <v>31.52</v>
-      </c>
-      <c r="E14" s="1">
-        <v>50.08</v>
-      </c>
-      <c r="F14" s="1">
-        <v>50.04</v>
-      </c>
-      <c r="G14" s="1">
+      <c r="C14" s="3">
+        <v>0.40000000000000568</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3.9999999999999147E-2</v>
+      </c>
+      <c r="E14" s="3">
         <v>6.4599999999999991</v>
       </c>
+      <c r="F14" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.62600000000000011</v>
+      </c>
       <c r="H14" s="2">
-        <v>7.6</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0.62600000000000011</v>
-      </c>
-      <c r="J14" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>14</v>
       </c>
-      <c r="C15" s="1">
-        <v>29.380000000000003</v>
-      </c>
-      <c r="D15" s="1">
-        <v>29.54</v>
-      </c>
-      <c r="E15" s="1">
-        <v>55.019999999999996</v>
-      </c>
-      <c r="F15" s="1">
-        <v>55.220000000000006</v>
-      </c>
-      <c r="G15" s="1">
+      <c r="C15" s="3">
+        <v>0.15999999999999659</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.20000000000000995</v>
+      </c>
+      <c r="E15" s="3">
         <v>8.42</v>
       </c>
+      <c r="F15" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1.002</v>
+      </c>
       <c r="H15" s="2">
-        <v>7.8</v>
-      </c>
-      <c r="I15" s="1">
-        <v>1.002</v>
-      </c>
-      <c r="J15" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>15</v>
       </c>
-      <c r="C16" s="1">
-        <v>33.58</v>
-      </c>
-      <c r="D16" s="1">
-        <v>33.559999999999988</v>
-      </c>
-      <c r="E16" s="1">
-        <v>47.620000000000005</v>
-      </c>
-      <c r="F16" s="1">
-        <v>46.82</v>
-      </c>
-      <c r="G16" s="1">
+      <c r="C16" s="3">
+        <v>2.0000000000010232E-2</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.80000000000000426</v>
+      </c>
+      <c r="E16" s="3">
         <v>13.34</v>
       </c>
+      <c r="F16" s="2">
+        <v>5</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.69399999999999995</v>
+      </c>
       <c r="H16" s="2">
-        <v>5</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0.69399999999999995</v>
-      </c>
-      <c r="J16" s="2">
         <v>4</v>
       </c>
     </row>

--- a/sin_patrones.xlsx
+++ b/sin_patrones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Avances_Tesis_FCB\Script_analisis_GLM\Script GLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E7672A-C80C-4785-839C-71C68C1F2B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8079BB-BC54-482D-BB65-A8C52BE01978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A02DA300-8EA0-4CC6-8739-25F8F4A91BC5}"/>
   </bookViews>
@@ -536,8 +536,8 @@
       <c r="E2" s="3">
         <v>18.36</v>
       </c>
-      <c r="F2" s="2">
-        <v>20</v>
+      <c r="F2" s="3">
+        <v>0.2</v>
       </c>
       <c r="G2" s="3">
         <v>0.71599999999999997</v>
@@ -562,8 +562,8 @@
       <c r="E3" s="3">
         <v>13.36</v>
       </c>
-      <c r="F3" s="2">
-        <v>58.2</v>
+      <c r="F3" s="3">
+        <v>0.58200000000000007</v>
       </c>
       <c r="G3" s="3">
         <v>0.752</v>
@@ -588,8 +588,8 @@
       <c r="E4" s="3">
         <v>16.600000000000001</v>
       </c>
-      <c r="F4" s="2">
-        <v>37.5</v>
+      <c r="F4" s="3">
+        <v>0.375</v>
       </c>
       <c r="G4" s="3">
         <v>0.89500000000000002</v>
@@ -614,8 +614,8 @@
       <c r="E5" s="3">
         <v>14</v>
       </c>
-      <c r="F5" s="2">
-        <v>24</v>
+      <c r="F5" s="3">
+        <v>0.24</v>
       </c>
       <c r="G5" s="3">
         <v>1.0925</v>
@@ -640,8 +640,8 @@
       <c r="E6" s="3">
         <v>10.739999999999998</v>
       </c>
-      <c r="F6" s="2">
-        <v>53.4</v>
+      <c r="F6" s="3">
+        <v>0.53400000000000003</v>
       </c>
       <c r="G6" s="3">
         <v>0.39600000000000002</v>
@@ -666,8 +666,8 @@
       <c r="E7" s="3">
         <v>7.76</v>
       </c>
-      <c r="F7" s="2">
-        <v>17.2</v>
+      <c r="F7" s="3">
+        <v>0.17199999999999999</v>
       </c>
       <c r="G7" s="3">
         <v>0.8</v>
@@ -692,8 +692,8 @@
       <c r="E8" s="3">
         <v>19.2</v>
       </c>
-      <c r="F8" s="2">
-        <v>26.6</v>
+      <c r="F8" s="3">
+        <v>0.26600000000000001</v>
       </c>
       <c r="G8" s="3">
         <v>0.56600000000000006</v>
@@ -718,8 +718,8 @@
       <c r="E9" s="3">
         <v>15.419999999999998</v>
       </c>
-      <c r="F9" s="2">
-        <v>43.8</v>
+      <c r="F9" s="3">
+        <v>0.43799999999999994</v>
       </c>
       <c r="G9" s="3">
         <v>0.42000000000000004</v>
@@ -744,8 +744,8 @@
       <c r="E10" s="3">
         <v>15</v>
       </c>
-      <c r="F10" s="2">
-        <v>3</v>
+      <c r="F10" s="3">
+        <v>0.03</v>
       </c>
       <c r="G10" s="3">
         <v>0.625</v>
@@ -770,8 +770,8 @@
       <c r="E11" s="3">
         <v>8.9</v>
       </c>
-      <c r="F11" s="2">
-        <v>34.200000000000003</v>
+      <c r="F11" s="3">
+        <v>0.34200000000000003</v>
       </c>
       <c r="G11" s="3">
         <v>0.20400000000000001</v>
@@ -796,8 +796,8 @@
       <c r="E12" s="3">
         <v>15.819999999999999</v>
       </c>
-      <c r="F12" s="2">
-        <v>24.4</v>
+      <c r="F12" s="3">
+        <v>0.24399999999999999</v>
       </c>
       <c r="G12" s="3">
         <v>0.61199999999999999</v>
@@ -822,8 +822,8 @@
       <c r="E13" s="3">
         <v>12.2</v>
       </c>
-      <c r="F13" s="2">
-        <v>11</v>
+      <c r="F13" s="3">
+        <v>0.11</v>
       </c>
       <c r="G13" s="3">
         <v>0.91500000000000004</v>
@@ -848,8 +848,8 @@
       <c r="E14" s="3">
         <v>6.4599999999999991</v>
       </c>
-      <c r="F14" s="2">
-        <v>7.6</v>
+      <c r="F14" s="3">
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="G14" s="3">
         <v>0.62600000000000011</v>
@@ -874,8 +874,8 @@
       <c r="E15" s="3">
         <v>8.42</v>
       </c>
-      <c r="F15" s="2">
-        <v>7.8</v>
+      <c r="F15" s="3">
+        <v>7.8E-2</v>
       </c>
       <c r="G15" s="3">
         <v>1.002</v>
@@ -900,8 +900,8 @@
       <c r="E16" s="3">
         <v>13.34</v>
       </c>
-      <c r="F16" s="2">
-        <v>5</v>
+      <c r="F16" s="3">
+        <v>0.05</v>
       </c>
       <c r="G16" s="3">
         <v>0.69399999999999995</v>

--- a/sin_patrones.xlsx
+++ b/sin_patrones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Avances_Tesis_FCB\Script_analisis_GLM\Script GLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8079BB-BC54-482D-BB65-A8C52BE01978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5287D3C8-8928-4168-88C3-CDC210918A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A02DA300-8EA0-4CC6-8739-25F8F4A91BC5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>sample</t>
   </si>
@@ -47,9 +47,6 @@
     <t>N_ind</t>
   </si>
   <si>
-    <t>Gru</t>
-  </si>
-  <si>
     <t>T_par</t>
   </si>
   <si>
@@ -105,6 +102,18 @@
   </si>
   <si>
     <t>V_hu</t>
+  </si>
+  <si>
+    <t>T_den</t>
+  </si>
+  <si>
+    <t>T_fue</t>
+  </si>
+  <si>
+    <t>H_den</t>
+  </si>
+  <si>
+    <t>H_fue</t>
   </si>
 </sst>
 </file>
@@ -488,425 +497,569 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B0D2D6-B11C-4A0B-A56C-C0F17EB0640F}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="8" width="11.42578125" style="1"/>
+    <col min="6" max="11" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1">
+        <v>23.580000000000002</v>
+      </c>
+      <c r="C2" s="1">
+        <v>27.22</v>
+      </c>
+      <c r="D2" s="1">
+        <v>55.3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>54.1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>3.639999999999997</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1.1999999999999957</v>
+      </c>
+      <c r="H2" s="3">
+        <v>18.36</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="K2" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1">
+        <v>23.779999999999998</v>
+      </c>
+      <c r="C3" s="1">
+        <v>27.419999999999998</v>
+      </c>
+      <c r="D3" s="1">
+        <v>52.319999999999993</v>
+      </c>
+      <c r="E3" s="1">
+        <v>51.6</v>
+      </c>
+      <c r="F3" s="3">
+        <v>3.6400000000000006</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.71999999999999176</v>
+      </c>
+      <c r="H3" s="3">
+        <v>13.36</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.58200000000000007</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.752</v>
+      </c>
+      <c r="K3" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1">
+        <v>23.924999999999997</v>
+      </c>
+      <c r="C4" s="1">
+        <v>27.3</v>
+      </c>
+      <c r="D4" s="1">
+        <v>52.3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>52.174999999999997</v>
+      </c>
+      <c r="F4" s="3">
+        <v>3.3750000000000036</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="H4" s="3">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="K4" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1">
+        <v>24.275000000000002</v>
+      </c>
+      <c r="C5" s="1">
+        <v>26.95</v>
+      </c>
+      <c r="D5" s="1">
+        <v>53.2</v>
+      </c>
+      <c r="E5" s="1">
+        <v>53.625</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2.6749999999999972</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.42499999999999716</v>
+      </c>
+      <c r="H5" s="3">
+        <v>14</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.24</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1.0925</v>
+      </c>
+      <c r="K5" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1">
+        <v>24.339999999999996</v>
+      </c>
+      <c r="C6" s="1">
+        <v>27.020000000000003</v>
+      </c>
+      <c r="D6" s="1">
+        <v>52.160000000000004</v>
+      </c>
+      <c r="E6" s="1">
+        <v>52.14</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2.6800000000000068</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2.0000000000003126E-2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>10.739999999999998</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="K6" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1">
+        <v>24.04</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26.740000000000002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>53.56</v>
+      </c>
+      <c r="E7" s="1">
+        <v>53.839999999999996</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2.7000000000000028</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.27999999999999403</v>
+      </c>
+      <c r="H7" s="3">
+        <v>7.76</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="K7" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1">
+        <v>22.32</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24.44</v>
+      </c>
+      <c r="D8" s="1">
+        <v>61.42</v>
+      </c>
+      <c r="E8" s="1">
+        <v>60.7</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2.120000000000001</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.71999999999999886</v>
+      </c>
+      <c r="H8" s="3">
+        <v>19.2</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.56600000000000006</v>
+      </c>
+      <c r="K8" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1">
+        <v>25.619999999999997</v>
+      </c>
+      <c r="D9" s="1">
+        <v>57.8</v>
+      </c>
+      <c r="E9" s="1">
+        <v>57.56</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2.6199999999999974</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.23999999999999488</v>
+      </c>
+      <c r="H9" s="3">
+        <v>15.419999999999998</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.43799999999999994</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.42000000000000004</v>
+      </c>
+      <c r="K9" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23.15</v>
+      </c>
+      <c r="C10" s="1">
+        <v>26.85</v>
+      </c>
+      <c r="D10" s="1">
+        <v>54.45</v>
+      </c>
+      <c r="E10" s="1">
+        <v>54.55</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3.7000000000000028</v>
+      </c>
+      <c r="G10" s="3">
+        <v>9.9999999999994316E-2</v>
+      </c>
+      <c r="H10" s="3">
+        <v>15</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="K10" s="2">
         <v>2</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1">
+        <v>24.080000000000002</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25.639999999999997</v>
+      </c>
+      <c r="D11" s="1">
+        <v>56.98</v>
+      </c>
+      <c r="E11" s="1">
+        <v>57.040000000000006</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1.5599999999999952</v>
+      </c>
+      <c r="G11" s="3">
+        <v>6.0000000000009379E-2</v>
+      </c>
+      <c r="H11" s="3">
+        <v>8.9</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.34200000000000003</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0.20400000000000001</v>
+      </c>
+      <c r="K11" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1">
+        <v>22.7</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25.479999999999997</v>
+      </c>
+      <c r="D12" s="1">
+        <v>58.42</v>
+      </c>
+      <c r="E12" s="1">
+        <v>58.08</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2.7799999999999976</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.34000000000000341</v>
+      </c>
+      <c r="H12" s="3">
+        <v>15.819999999999999</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="K12" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1">
+        <v>23.75</v>
+      </c>
+      <c r="C13" s="1">
+        <v>26.75</v>
+      </c>
+      <c r="D13" s="1">
+        <v>53.7</v>
+      </c>
+      <c r="E13" s="1">
+        <v>53.95</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="H13" s="3">
+        <v>12.2</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="K13" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="1">
+        <v>31.920000000000005</v>
+      </c>
+      <c r="C14" s="1">
+        <v>31.52</v>
+      </c>
+      <c r="D14" s="1">
+        <v>50.08</v>
+      </c>
+      <c r="E14" s="1">
+        <v>50.04</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.40000000000000568</v>
+      </c>
+      <c r="G14" s="3">
+        <v>3.9999999999999147E-2</v>
+      </c>
+      <c r="H14" s="3">
+        <v>6.4599999999999991</v>
+      </c>
+      <c r="I14" s="3">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.62600000000000011</v>
+      </c>
+      <c r="K14" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="1">
+        <v>29.380000000000003</v>
+      </c>
+      <c r="C15" s="1">
+        <v>29.54</v>
+      </c>
+      <c r="D15" s="1">
+        <v>55.019999999999996</v>
+      </c>
+      <c r="E15" s="1">
+        <v>55.220000000000006</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.15999999999999659</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.20000000000000995</v>
+      </c>
+      <c r="H15" s="3">
+        <v>8.42</v>
+      </c>
+      <c r="I15" s="3">
+        <v>7.8E-2</v>
+      </c>
+      <c r="J15" s="3">
+        <v>1.002</v>
+      </c>
+      <c r="K15" s="2">
         <v>6</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3">
-        <v>3.639999999999997</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1.1999999999999957</v>
-      </c>
-      <c r="E2" s="3">
-        <v>18.36</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.71599999999999997</v>
-      </c>
-      <c r="H2" s="2">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3">
-        <v>3.6400000000000006</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0.71999999999999176</v>
-      </c>
-      <c r="E3" s="3">
-        <v>13.36</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.58200000000000007</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.752</v>
-      </c>
-      <c r="H3" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3">
-        <v>3.3750000000000036</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.125</v>
-      </c>
-      <c r="E4" s="3">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0.89500000000000002</v>
-      </c>
-      <c r="H4" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" s="3">
-        <v>2.6749999999999972</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0.42499999999999716</v>
-      </c>
-      <c r="E5" s="3">
-        <v>14</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.24</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1.0925</v>
-      </c>
-      <c r="H5" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6" s="3">
-        <v>2.6800000000000068</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2.0000000000003126E-2</v>
-      </c>
-      <c r="E6" s="3">
-        <v>10.739999999999998</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0.53400000000000003</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0.39600000000000002</v>
-      </c>
-      <c r="H6" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3">
-        <v>2.7000000000000028</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0.27999999999999403</v>
-      </c>
-      <c r="E7" s="3">
-        <v>7.76</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.17199999999999999</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="H7" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3">
-        <v>2.120000000000001</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0.71999999999999886</v>
-      </c>
-      <c r="E8" s="3">
-        <v>19.2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.26600000000000001</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0.56600000000000006</v>
-      </c>
-      <c r="H8" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9" s="3">
-        <v>2.6199999999999974</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0.23999999999999488</v>
-      </c>
-      <c r="E9" s="3">
-        <v>15.419999999999998</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.43799999999999994</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0.42000000000000004</v>
-      </c>
-      <c r="H9" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10" s="3">
-        <v>3.7000000000000028</v>
-      </c>
-      <c r="D10" s="3">
-        <v>9.9999999999994316E-2</v>
-      </c>
-      <c r="E10" s="3">
-        <v>15</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0.625</v>
-      </c>
-      <c r="H10" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1.5599999999999952</v>
-      </c>
-      <c r="D11" s="3">
-        <v>6.0000000000009379E-2</v>
-      </c>
-      <c r="E11" s="3">
-        <v>8.9</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0.34200000000000003</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0.20400000000000001</v>
-      </c>
-      <c r="H11" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12">
-        <v>11</v>
-      </c>
-      <c r="C12" s="3">
-        <v>2.7799999999999976</v>
-      </c>
-      <c r="D12" s="3">
-        <v>0.34000000000000341</v>
-      </c>
-      <c r="E12" s="3">
-        <v>15.819999999999999</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0.61199999999999999</v>
-      </c>
-      <c r="H12" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13">
-        <v>12</v>
-      </c>
-      <c r="C13" s="3">
-        <v>3</v>
-      </c>
-      <c r="D13" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>12.2</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0.11</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0.91500000000000004</v>
-      </c>
-      <c r="H13" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14">
-        <v>13</v>
-      </c>
-      <c r="C14" s="3">
-        <v>0.40000000000000568</v>
-      </c>
-      <c r="D14" s="3">
-        <v>3.9999999999999147E-2</v>
-      </c>
-      <c r="E14" s="3">
-        <v>6.4599999999999991</v>
-      </c>
-      <c r="F14" s="3">
-        <v>7.5999999999999998E-2</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0.62600000000000011</v>
-      </c>
-      <c r="H14" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15">
-        <v>14</v>
-      </c>
-      <c r="C15" s="3">
-        <v>0.15999999999999659</v>
-      </c>
-      <c r="D15" s="3">
-        <v>0.20000000000000995</v>
-      </c>
-      <c r="E15" s="3">
-        <v>8.42</v>
-      </c>
-      <c r="F15" s="3">
-        <v>7.8E-2</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1.002</v>
-      </c>
-      <c r="H15" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16">
-        <v>15</v>
-      </c>
-      <c r="C16" s="3">
+      <c r="B16" s="1">
+        <v>33.58</v>
+      </c>
+      <c r="C16" s="1">
+        <v>33.559999999999988</v>
+      </c>
+      <c r="D16" s="1">
+        <v>47.620000000000005</v>
+      </c>
+      <c r="E16" s="1">
+        <v>46.82</v>
+      </c>
+      <c r="F16" s="3">
         <v>2.0000000000010232E-2</v>
       </c>
-      <c r="D16" s="3">
+      <c r="G16" s="3">
         <v>0.80000000000000426</v>
       </c>
-      <c r="E16" s="3">
+      <c r="H16" s="3">
         <v>13.34</v>
       </c>
-      <c r="F16" s="3">
+      <c r="I16" s="3">
         <v>0.05</v>
       </c>
-      <c r="G16" s="3">
+      <c r="J16" s="3">
         <v>0.69399999999999995</v>
       </c>
-      <c r="H16" s="2">
+      <c r="K16" s="2">
         <v>4</v>
       </c>
     </row>
